--- a/GHG_Calculation/output/continent_emission_95PI.xlsx
+++ b/GHG_Calculation/output/continent_emission_95PI.xlsx
@@ -622,16 +622,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>199.3571773222749</v>
+        <v>194.1602742900667</v>
       </c>
       <c r="C2" t="n">
-        <v>140.7249108136577</v>
+        <v>138.1349950344108</v>
       </c>
       <c r="D2" t="n">
-        <v>183.8831097566248</v>
+        <v>179.7966480743407</v>
       </c>
       <c r="E2" t="n">
-        <v>420.2716008758476</v>
+        <v>408.7868515128409</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -646,76 +646,76 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>199.3571773222749</v>
+        <v>194.1602742900667</v>
       </c>
       <c r="K2" t="n">
-        <v>140.7249108136577</v>
+        <v>138.1349950344108</v>
       </c>
       <c r="L2" t="n">
-        <v>183.8831097566248</v>
+        <v>179.7966480743407</v>
       </c>
       <c r="M2" t="n">
-        <v>420.2716008758476</v>
+        <v>408.7868515128409</v>
       </c>
       <c r="N2" t="n">
-        <v>14.13595863044106</v>
+        <v>14.18660154287263</v>
       </c>
       <c r="O2" t="n">
-        <v>9.566717688906889</v>
+        <v>9.568028100609103</v>
       </c>
       <c r="P2" t="n">
-        <v>12.6506978525485</v>
+        <v>12.66004709557657</v>
       </c>
       <c r="Q2" t="n">
-        <v>26.96705140268773</v>
+        <v>27.87398796152752</v>
       </c>
       <c r="R2" t="n">
-        <v>9241.760493811831</v>
+        <v>9115.26962703603</v>
       </c>
       <c r="S2" t="n">
-        <v>7053.001368869895</v>
+        <v>6980.412849292583</v>
       </c>
       <c r="T2" t="n">
-        <v>8762.066387179539</v>
+        <v>8628.853367791864</v>
       </c>
       <c r="U2" t="n">
-        <v>14847.76174386303</v>
+        <v>14567.56639212167</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05643604556281877</v>
+        <v>0.05496485370381123</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03983783069753473</v>
+        <v>0.03910465115072985</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05205549004980899</v>
+        <v>0.05089865315640091</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1189747343655732</v>
+        <v>0.1157235153874853</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.05643604556281877</v>
+        <v>0.05496485370381123</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.03983783069753473</v>
+        <v>0.03910465115072985</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05205549004980899</v>
+        <v>0.05089865315640091</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1189747343655732</v>
+        <v>0.1157235153874853</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.004871864940601867</v>
+        <v>0.004889318686471924</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.00329710617607877</v>
+        <v>0.003297557800832115</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.004359979606141176</v>
+        <v>0.004363201761109256</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.009294016466434976</v>
+        <v>0.009606586171813621</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
@@ -737,100 +737,100 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>787.1646277092194</v>
+        <v>782.4917825491472</v>
       </c>
       <c r="C3" t="n">
-        <v>703.0284703071126</v>
+        <v>700.1604312631003</v>
       </c>
       <c r="D3" t="n">
-        <v>778.3988131718456</v>
+        <v>773.0877444059664</v>
       </c>
       <c r="E3" t="n">
-        <v>915.8161547612204</v>
+        <v>914.9087168055183</v>
       </c>
       <c r="F3" t="n">
-        <v>20.04943055157243</v>
+        <v>21.22088511143491</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8255250211601781</v>
+        <v>0.9950968397064949</v>
       </c>
       <c r="H3" t="n">
-        <v>18.31206343721317</v>
+        <v>19.37930030343847</v>
       </c>
       <c r="I3" t="n">
-        <v>49.29555441465445</v>
+        <v>51.38124873882462</v>
       </c>
       <c r="J3" t="n">
-        <v>807.2140582607918</v>
+        <v>803.712667660582</v>
       </c>
       <c r="K3" t="n">
-        <v>718.1202774072424</v>
+        <v>715.9068530346317</v>
       </c>
       <c r="L3" t="n">
-        <v>799.1706277650417</v>
+        <v>795.3027242749745</v>
       </c>
       <c r="M3" t="n">
-        <v>940.2796094360253</v>
+        <v>939.5162399565776</v>
       </c>
       <c r="N3" t="n">
-        <v>147.4383453795878</v>
+        <v>147.6820166291753</v>
       </c>
       <c r="O3" t="n">
-        <v>136.4655416293269</v>
+        <v>136.6903428234775</v>
       </c>
       <c r="P3" t="n">
-        <v>147.055390915834</v>
+        <v>147.401979528195</v>
       </c>
       <c r="Q3" t="n">
-        <v>160.2134591622763</v>
+        <v>160.3268557459346</v>
       </c>
       <c r="R3" t="n">
-        <v>62045.44786166887</v>
+        <v>62017.4325666006</v>
       </c>
       <c r="S3" t="n">
-        <v>58324.64162454192</v>
+        <v>58223.75993503039</v>
       </c>
       <c r="T3" t="n">
-        <v>61937.02399289265</v>
+        <v>61870.7755734735</v>
       </c>
       <c r="U3" t="n">
-        <v>66484.84247240733</v>
+        <v>66549.94914553929</v>
       </c>
       <c r="V3" t="n">
-        <v>0.03241536855592469</v>
+        <v>0.03222294121260094</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02895064916297445</v>
+        <v>0.02883254357315013</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0320543931018462</v>
+        <v>0.03183568376784977</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03771322686646559</v>
+        <v>0.03767585865308268</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.03324100230239649</v>
+        <v>0.03309681535246411</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02957212842170245</v>
+        <v>0.02948097980515747</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.03290977455816656</v>
+        <v>0.03275049464040126</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.03872062972924755</v>
+        <v>0.03868919424275643</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.00617853984224533</v>
+        <v>0.006188751110691881</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.005718714381117278</v>
+        <v>0.00572813488248731</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.006162491782251325</v>
+        <v>0.006177015897703297</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.006713892767512805</v>
+        <v>0.006718644755934155</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -852,100 +852,100 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>299.8241901171431</v>
+        <v>296.1274804785132</v>
       </c>
       <c r="C4" t="n">
-        <v>286.7262881227966</v>
+        <v>283.6106588085821</v>
       </c>
       <c r="D4" t="n">
-        <v>299.2758835327021</v>
+        <v>295.7130338416259</v>
       </c>
       <c r="E4" t="n">
-        <v>316.0740286825979</v>
+        <v>311.3630496163282</v>
       </c>
       <c r="F4" t="n">
-        <v>53.77920929281878</v>
+        <v>55.02968809350311</v>
       </c>
       <c r="G4" t="n">
-        <v>2.220599750171565</v>
+        <v>2.588807132399823</v>
       </c>
       <c r="H4" t="n">
-        <v>49.12366625972516</v>
+        <v>50.27282634975847</v>
       </c>
       <c r="I4" t="n">
-        <v>132.1919096134361</v>
+        <v>133.1723774291662</v>
       </c>
       <c r="J4" t="n">
-        <v>353.6033994099619</v>
+        <v>351.1571685720164</v>
       </c>
       <c r="K4" t="n">
-        <v>298.6800033794994</v>
+        <v>295.3674628076202</v>
       </c>
       <c r="L4" t="n">
-        <v>349.4601158683654</v>
+        <v>346.1630629624254</v>
       </c>
       <c r="M4" t="n">
-        <v>433.2853985466524</v>
+        <v>431.0830548320528</v>
       </c>
       <c r="N4" t="n">
-        <v>39.91551083126721</v>
+        <v>39.74388982305398</v>
       </c>
       <c r="O4" t="n">
-        <v>37.97720579487647</v>
+        <v>37.77080186671866</v>
       </c>
       <c r="P4" t="n">
-        <v>39.86363710174123</v>
+        <v>39.71658075904384</v>
       </c>
       <c r="Q4" t="n">
-        <v>42.11949550859234</v>
+        <v>41.93666111974341</v>
       </c>
       <c r="R4" t="n">
-        <v>20444.22624100492</v>
+        <v>20331.32547313818</v>
       </c>
       <c r="S4" t="n">
-        <v>18834.61970606066</v>
+        <v>18652.61748076243</v>
       </c>
       <c r="T4" t="n">
-        <v>20345.1198660191</v>
+        <v>20214.28161215377</v>
       </c>
       <c r="U4" t="n">
-        <v>22649.91789675394</v>
+        <v>22581.7779610999</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02713438257939464</v>
+        <v>0.02679982673991976</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02594900963279165</v>
+        <v>0.02566704213125535</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02708476029699238</v>
+        <v>0.0267623189137512</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02860500886980897</v>
+        <v>0.02817866065468417</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03200145364260184</v>
+        <v>0.03178006735816498</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02703083256006711</v>
+        <v>0.02673104439703724</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03162648242794214</v>
+        <v>0.03132809591383423</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.03921275253219845</v>
+        <v>0.03901343827106454</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.00617268569814418</v>
+        <v>0.006146145575749728</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.005872938869715825</v>
+        <v>0.005841019784907761</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.00616466374823834</v>
+        <v>0.006141922398710664</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.006513518231997082</v>
+        <v>0.006485244029972022</v>
       </c>
       <c r="AH4" t="n">
         <v>1</v>
@@ -967,100 +967,100 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>370.295457037203</v>
+        <v>367.9553864440433</v>
       </c>
       <c r="C5" t="n">
-        <v>353.6252153767715</v>
+        <v>351.3586082857258</v>
       </c>
       <c r="D5" t="n">
-        <v>370.0843411301353</v>
+        <v>367.7015874593954</v>
       </c>
       <c r="E5" t="n">
-        <v>388.7877867112978</v>
+        <v>385.718433517517</v>
       </c>
       <c r="F5" t="n">
-        <v>83.52261410565791</v>
+        <v>82.43739317125477</v>
       </c>
       <c r="G5" t="n">
-        <v>3.443262653233262</v>
+        <v>3.86790791080356</v>
       </c>
       <c r="H5" t="n">
-        <v>76.21615370426518</v>
+        <v>75.24607911823955</v>
       </c>
       <c r="I5" t="n">
-        <v>205.2813314843808</v>
+        <v>199.588204012685</v>
       </c>
       <c r="J5" t="n">
-        <v>453.8180711428609</v>
+        <v>450.392779615298</v>
       </c>
       <c r="K5" t="n">
-        <v>369.962480527363</v>
+        <v>367.5282813754221</v>
       </c>
       <c r="L5" t="n">
-        <v>446.5599447647706</v>
+        <v>443.5187955941674</v>
       </c>
       <c r="M5" t="n">
-        <v>576.399683627609</v>
+        <v>569.8947520248257</v>
       </c>
       <c r="N5" t="n">
-        <v>26.78541547712978</v>
+        <v>26.73713145998103</v>
       </c>
       <c r="O5" t="n">
-        <v>24.40272928119821</v>
+        <v>24.32223273306472</v>
       </c>
       <c r="P5" t="n">
-        <v>26.76798739495189</v>
+        <v>26.70356954635768</v>
       </c>
       <c r="Q5" t="n">
-        <v>29.33946493839868</v>
+        <v>29.3397659173006</v>
       </c>
       <c r="R5" t="n">
-        <v>19565.50634611367</v>
+        <v>19459.84193818787</v>
       </c>
       <c r="S5" t="n">
-        <v>17141.32909079757</v>
+        <v>17063.84778941511</v>
       </c>
       <c r="T5" t="n">
-        <v>19381.52482673021</v>
+        <v>19299.24568752607</v>
       </c>
       <c r="U5" t="n">
-        <v>22927.38360613195</v>
+        <v>22742.52247598162</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03225606731177087</v>
+        <v>0.03205222610029288</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0308039392154536</v>
+        <v>0.03060649733624966</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03223767721602558</v>
+        <v>0.03203011792430292</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03386691567456656</v>
+        <v>0.03359954738435217</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03953163878165387</v>
+        <v>0.03923326505879072</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03222706206066524</v>
+        <v>0.03201502140447276</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03889939064422805</v>
+        <v>0.03863447917829489</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.05020960057770203</v>
+        <v>0.04964296248465959</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.004308543054298289</v>
+        <v>0.004300776373699384</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.003925278285871653</v>
+        <v>0.003912330088609165</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.004305739676374903</v>
+        <v>0.004295377803348503</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.004719372301135252</v>
+        <v>0.004719420714816142</v>
       </c>
       <c r="AH5" t="n">
         <v>1</v>
@@ -1082,100 +1082,100 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.93529473035575</v>
+        <v>26.38378764560866</v>
       </c>
       <c r="C6" t="n">
-        <v>23.25960535770996</v>
+        <v>22.78463603324555</v>
       </c>
       <c r="D6" t="n">
-        <v>26.67663880930909</v>
+        <v>26.16481097366968</v>
       </c>
       <c r="E6" t="n">
-        <v>32.07260439319585</v>
+        <v>31.17320896171821</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02239755802491167</v>
+        <v>0.02215865566344319</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000928821422256146</v>
+        <v>0.001030046468293444</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02046093828933026</v>
+        <v>0.02022940552167796</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05510420178826696</v>
+        <v>0.05389783952446833</v>
       </c>
       <c r="J6" t="n">
-        <v>26.95769228838066</v>
+        <v>26.4059463012721</v>
       </c>
       <c r="K6" t="n">
-        <v>23.28007693828508</v>
+        <v>22.80365727157907</v>
       </c>
       <c r="L6" t="n">
-        <v>26.69852932897892</v>
+        <v>26.18711305393834</v>
       </c>
       <c r="M6" t="n">
-        <v>32.08954981180377</v>
+        <v>31.20355328145466</v>
       </c>
       <c r="N6" t="n">
-        <v>1.635704876465436</v>
+        <v>1.640722549278314</v>
       </c>
       <c r="O6" t="n">
-        <v>1.282459296053418</v>
+        <v>1.282013930635196</v>
       </c>
       <c r="P6" t="n">
-        <v>1.622417551501642</v>
+        <v>1.626850217631626</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.068963348058198</v>
+        <v>2.077750993520789</v>
       </c>
       <c r="R6" t="n">
-        <v>1174.405123061342</v>
+        <v>1160.877806087326</v>
       </c>
       <c r="S6" t="n">
-        <v>1039.95093490348</v>
+        <v>1026.357311491727</v>
       </c>
       <c r="T6" t="n">
-        <v>1169.619596453978</v>
+        <v>1155.044238843231</v>
       </c>
       <c r="U6" t="n">
-        <v>1339.629995178928</v>
+        <v>1320.728988412411</v>
       </c>
       <c r="V6" t="n">
-        <v>0.04096410808647138</v>
+        <v>0.04012535744140888</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03537399525270816</v>
+        <v>0.03465164582457322</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04057073540527252</v>
+        <v>0.03979233030554409</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0487771025388798</v>
+        <v>0.04740927151878679</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.04099817105095684</v>
+        <v>0.04015905707509527</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03540512912548643</v>
+        <v>0.03468057396777095</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.04060402724866244</v>
+        <v>0.03982624806422556</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.04880287370516458</v>
+        <v>0.04745542018751078</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.004229920952150452</v>
+        <v>0.004242896617667873</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.003316430442133674</v>
+        <v>0.003315278730390924</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.004195560026123361</v>
+        <v>0.004207022868599948</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.005350324218690225</v>
+        <v>0.005373049006148586</v>
       </c>
       <c r="AH6" t="n">
         <v>1</v>
@@ -1197,100 +1197,100 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110.4882504548207</v>
+        <v>107.9351771739409</v>
       </c>
       <c r="C7" t="n">
-        <v>96.64350140519863</v>
+        <v>94.97882712803731</v>
       </c>
       <c r="D7" t="n">
-        <v>109.5190218184176</v>
+        <v>106.9518137044942</v>
       </c>
       <c r="E7" t="n">
-        <v>130.4246962869562</v>
+        <v>126.5809481696536</v>
       </c>
       <c r="F7" t="n">
-        <v>9.372299407413559</v>
+        <v>11.51463093660173</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3886674159663764</v>
+        <v>0.5385721034273971</v>
       </c>
       <c r="H7" t="n">
-        <v>8.591382931438094</v>
+        <v>10.53292932522566</v>
       </c>
       <c r="I7" t="n">
-        <v>22.93371047839313</v>
+        <v>28.08610443701281</v>
       </c>
       <c r="J7" t="n">
-        <v>119.8605498622343</v>
+        <v>119.4498081105426</v>
       </c>
       <c r="K7" t="n">
-        <v>102.3437855125271</v>
+        <v>100.7240287692089</v>
       </c>
       <c r="L7" t="n">
-        <v>119.0663344114358</v>
+        <v>118.4847127561239</v>
       </c>
       <c r="M7" t="n">
-        <v>143.5168676453999</v>
+        <v>144.005431949319</v>
       </c>
       <c r="N7" t="n">
-        <v>7.816609994699083</v>
+        <v>7.727642272033632</v>
       </c>
       <c r="O7" t="n">
-        <v>6.445810690461315</v>
+        <v>6.35237005115103</v>
       </c>
       <c r="P7" t="n">
-        <v>7.753192824690141</v>
+        <v>7.664120539909224</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.616997070829997</v>
+        <v>9.449849760620067</v>
       </c>
       <c r="R7" t="n">
-        <v>5370.169374833174</v>
+        <v>5334.791159249833</v>
       </c>
       <c r="S7" t="n">
-        <v>4766.986755747892</v>
+        <v>4710.864907695614</v>
       </c>
       <c r="T7" t="n">
-        <v>5344.907320629486</v>
+        <v>5315.587115886461</v>
       </c>
       <c r="U7" t="n">
-        <v>6117.804304575166</v>
+        <v>6086.023533936494</v>
       </c>
       <c r="V7" t="n">
-        <v>0.04288345682921693</v>
+        <v>0.04189254053384844</v>
       </c>
       <c r="W7" t="n">
-        <v>0.037509937964208</v>
+        <v>0.03686383317745019</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0425072731697261</v>
+        <v>0.04151087076610524</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.05062132678960692</v>
+        <v>0.04912946493305476</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.04652109789398028</v>
+        <v>0.04636167799092166</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03972237129014655</v>
+        <v>0.03909370020439776</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.04621284155127225</v>
+        <v>0.04598709856915577</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.05570275004447243</v>
+        <v>0.05589237496973974</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.004084690017068437</v>
+        <v>0.004038198562478875</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.00336835771480165</v>
+        <v>0.003319528868685744</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.004051550397537474</v>
+        <v>0.004005004302403033</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.005025510030055933</v>
+        <v>0.004938164627143755</v>
       </c>
       <c r="AH7" t="n">
         <v>1</v>
